--- a/frontend/data-source/patents.xlsx
+++ b/frontend/data-source/patents.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15080"/>
+    <workbookView windowWidth="30240" windowHeight="14640"/>
   </bookViews>
   <sheets>
     <sheet name="专利" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,13 @@
     <t>inventors</t>
   </si>
   <si>
-    <t>public_number</t>
-  </si>
-  <si>
-    <t>application_number</t>
-  </si>
-  <si>
-    <t>application_date</t>
+    <t>public_number（公开号）</t>
+  </si>
+  <si>
+    <t>application_number（申请号）</t>
+  </si>
+  <si>
+    <t>application_date（申请日）</t>
   </si>
   <si>
     <t>applicants</t>
@@ -1210,7 +1210,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1652,9 +1652,9 @@
     <tableColumn id="1" name="patent_id"/>
     <tableColumn id="2" name="patent_name"/>
     <tableColumn id="3" name="inventors"/>
-    <tableColumn id="4" name="public_number"/>
-    <tableColumn id="5" name="application_number"/>
-    <tableColumn id="6" name="application_date"/>
+    <tableColumn id="4" name="public_number（公开号）"/>
+    <tableColumn id="5" name="application_number（申请号）"/>
+    <tableColumn id="6" name="application_date（申请日）"/>
     <tableColumn id="7" name="applicants"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
